--- a/outputs/evaluation/architecture/validation/CF_M06/run_2/CF_M06_arch_eval_gt_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_2/CF_M06_arch_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,326 +481,341 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CF_M06_AU11</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>CF_M06_AU01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Mobile device</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>This is the device where the application will be hosted.</t>
+        </is>
+      </c>
       <c r="E2" t="n">
-        <v>47</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CF_M06_AU09, CF_M06_AU07</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>dispatcher, store</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AU_01</t>
+          <t>AU_07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Mobile Device</t>
+          <t>React Native</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>The physical device where the application is hosted, either iOS or Android.</t>
+          <t>Framework used to develop the mobile application.</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.7089</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CF_M06_AU12</t>
+          <t>CF_M06_AU07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Store</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
+          <t>This is the component that contains the state and logic of the application.</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CF_M06_P02</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>AU_01</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Partner</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>A Javascript object that indicates an intention to modify the application state.</t>
+          <t>Third-party companies that offer digital signage service/consultancy using Waapiti technology.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7607</v>
+        <v>0.6647999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CF_M06_AU20</t>
+          <t>CF_M06_AU08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Firebase Cloud Messaging</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
+          <t xml:space="preserve"> is a Javascript object that indicates an intention to modify the state of the application.</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>91</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CF_M06_P02</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>The mobile application uses AWS SNS for push notifications.</t>
+          <t>Computer equipment that acts as an intermediary between the Waapiti platform and the audiovisual support.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.6817</v>
+        <v>0.7835</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CF_M06_AU21</t>
+          <t>CF_M06_AU09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apple Push Notification Service</t>
+          <t>Dispatcher</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
+          <t>This is the central hub that manages all the data flow.</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>91</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CF_M06_P02</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AU_23</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>AU_01</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>The mobile application uses AWS SNS for push notifications.</t>
+          <t>Third-party companies that offer digital signage service/consultancy using Waapiti technology.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8003</v>
+        <v>0.6454</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CF_M06_AU23</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Mobile Application</t>
-        </is>
-      </c>
+          <t>CF_M06_AU10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>The project “Development of a mobile application for a digital signage company”</t>
+          <t>With the data obtained, the Dispatcher notifies the Stores that need to be modified, thus updating the components.</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CF_M06_AU08, CF_M06_AU07</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>action, store</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AU_01</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Mobile Device</t>
-        </is>
-      </c>
+          <t>AU_15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>The physical device where the application is hosted, either iOS or Android.</t>
+          <t>The application uses sockets to show content in real time from the server.</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.8665</v>
+        <v>0.6262</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CF_M06_AU24</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Player</t>
-        </is>
-      </c>
+          <t>CF_M06_AU11</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Device</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">these are computer equipment that act as an intermediary between the Waapiti platform and the audiovisual media itself, thus allowing the synchronization or reproduction of client
-content. </t>
+          <t>This is the central hub that manages all the data flow. It notifies the Stores when the state needs to be modified.</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CF_M06_AU09, CF_M06_AU07</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>dispatcher, store</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AU_07</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>A Javascript object that indicates an intention to modify the application state.</t>
+          <t>The Waapiti server communicates with the database and other services hosted on AWS.</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.7835</v>
+        <v>0.6307</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CF_M06_AU25</t>
+          <t>CF_M06_AU12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Redux</t>
+          <t>User</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Redux [19] is a library used to manage application state. It is inspired by the Flux architecture, but with a simpler implementation.</t>
+          <t>As already mentioned, there are third-party companies that offer digital signage consulting using Waapiti technology. They are end users of this project.</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>CF_M06_AU23</t>
-        </is>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AU_10</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Player</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Library for building user interfaces using Javascript.</t>
+          <t>Computer equipment that acts as an intermediary between the Waapiti platform and the audiovisual support.</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0.7194</v>
+        <v>0.7565</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CF_M06_AU26</t>
+          <t>CF_M06_AU13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -811,102 +826,101 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>The requirement will be understood as complete if the communications between the server and the application use the minimum possible information.
-and authenticated.</t>
+          <t>Presentation: This is the layer that communicates with the user</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CF_M06_AU02, CF_M06_AU23</t>
+          <t>CF_M06_AU03, CF_M06_AU12</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>waapiti server, mobile application</t>
+          <t>presentation, user</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Presentation Layer</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Communication protocol used by the mobile application to interact with the Waapiti API.</t>
+          <t>The layer that communicates with the user, displaying system data and collecting user input.</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0.6449</v>
+        <v>0.8952</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M06_AU30</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>CF_M06_AU14</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>React</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>This functionality connects via socket [25] with the server and displays</t>
+          <t>is a library for building user interfaces using Javascript.</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CF_M06_AU23, CF_M06_AU02</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>mobile application, waapiti server</t>
-        </is>
-      </c>
+          <t>CF_M06_AU23</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>AU_17</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>HTTP</t>
+          <t>Redux</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Communication protocol used by the mobile application to interact with the Waapiti API.</t>
+          <t>Library used to manage the application state.</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.6713</v>
+        <v>0.7194</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M06_AU31</t>
+          <t>CF_M06_AU15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Socket</t>
+          <t>Expo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -916,36 +930,455 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>the content according to the messages that it sends.</t>
+          <t>is an open source framework for native Android, iOS and Web applications.</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CF_M06_AU30</t>
+          <t>CF_M06_AU23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>AU_07</t>
+          <t>P_03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Action</t>
+          <t>Observer</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A Javascript object that indicates an intention to modify the application state.</t>
+          <t>Design pattern to observe the state of an object in a program, reflected in the Flux architecture where stores act as subjects.</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.6631</v>
+        <v>0.6337</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M06_AU16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Jest</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>is a testing framework for Javascript. It is also the libraryrecommended for React projects. [20]</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>51</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CF_M06_AU23</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AU_02</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Computer equipment that acts as an intermediary between the Waapiti platform and the audiovisual support.</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6353</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CF_M06_AU17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NodeJS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>is a Javascript runtime environment that allows you to run it outside of the browser. In this case it is used to compile.</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>51</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Progressive NodeJS framework for building efficient, reliable, and scalable backend applications.</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0.744</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CF_M06_AU18</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>it is a programming language developed and maintained by Microsoft</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>51</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>AU_10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NestJS</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Progressive NodeJS framework for building efficient, reliable, and scalable backend applications.</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6955</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CF_M06_AU20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>91</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>The application uses AWS SNS for the delivery of push notifications.</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6879</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CF_M06_AU21</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Apple Push Notification Service</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Firebase Cloud Messaging (FCM) for Android devices and Apple Push Notification Service (APNS) for iOS devices.</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>91</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>AU_13</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>The application uses AWS SNS for the delivery of push notifications.</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>0.8037</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CF_M06_AU23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Mobile Application</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>The project “Development of a mobile application for a digital signage company”</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>AU_11</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>The mobile application interacts with the Waapiti API using HTTP requests.</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>0.7667</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CF_M06_AU26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>The requirement will be understood as complete if the communications between the server and the application use the minimum possible information.
+and authenticated.</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>43</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>CF_M06_AU02, CF_M06_AU23</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>waapiti server, mobile application</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Aquesta interactuar` a amb l’API de Waapiti mitjan¸ cant peticions HTTP.</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6449</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CF_M06_P01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Three Layers</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Architectural Pattern</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>This architecture follows the 3-layer model</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>45</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CF_M06_AU23</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>P_01</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>3-Layer Architecture</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>The architecture follows the 3-layer model: Presentation, Domain, and Data.</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8511</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CF_M06_P05</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Lazy Loading</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Design Pattern</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>The concept of Lazy Loading consists of loading objects/components only when they are needed. In this way, we achieve optimized efficiency. In this project, thanks to the React Navigation library, used to manage the application's navigation, this concept has been implemented.</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>49</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>CF_M06_AU23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>AU_16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>HTTP</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Aquesta interactuar` a amb l’API de Waapiti mitjan¸ cant peticions HTTP.</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6162</v>
       </c>
     </row>
   </sheetData>
